--- a/objetivos_mensuales/PLANTILLA.xlsx
+++ b/objetivos_mensuales/PLANTILLA.xlsx
@@ -3028,7 +3028,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Una fila por objetivo. El archivo se llama como el mes comercial (2026-10.xlsx) y va en la carpeta objetivos_mensuales del repo tablero_quo.</t>
+          <t>Una fila por objetivo. El archivo se llama con el mes comercial: «2026-10 objetivos.xlsx» y va en la carpeta objetivos_mensuales del repo tablero_quo.</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Copiar el archivo del mes anterior, renombrarlo (2026-11.xlsx), cambiar MES_COMERCIAL en todas las filas y ajustar los numeros.</t>
+          <t>Copiar el archivo del mes anterior, renombrarlo («2026-11 objetivos.xlsx»), cambiar MES_COMERCIAL en todas las filas y ajustar los numeros.</t>
         </is>
       </c>
     </row>
